--- a/docs/TEST_CHECKLIST.xlsx
+++ b/docs/TEST_CHECKLIST.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>생성일시: 2026-05-12 13:45:00</t>
+          <t>생성일시: 2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -582,10 +582,10 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>2</v>
@@ -658,10 +658,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>3</v>
@@ -696,10 +696,10 @@
         <v>26</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>79</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>35</v>
@@ -1098,7 +1098,7 @@
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1452,13 +1452,13 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (16ms) :: </t>
+          <t xml:space="preserve">status=401 (14ms) :: </t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1505,13 +1505,13 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (18ms) :: </t>
+          <t xml:space="preserve">status=401 (14ms) :: </t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1664,13 +1664,13 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (14ms) :: </t>
+          <t xml:space="preserve">status=401 (3ms) :: </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1823,13 +1823,13 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=204 (15ms) :: </t>
+          <t xml:space="preserve">status=204 (2ms) :: </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2225,13 +2225,13 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>status=200 (439ms) :: {"token":"eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1laWRlbnRpZmllc</t>
+          <t>status=200 (400ms) :: {"token":"eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJodHRwOi8vc2NoZW1hcy54bWxzb2FwLm9yZy93cy8yMDA1LzA1L2lkZW50aXR5L2NsYWltcy9uYW1laWRlbnRpZmllc</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2278,13 +2278,13 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>status=401 (328ms) :: {"message":"Invalid email or password","errorCode":"UNAUTHORIZED","details":null,"timestamp":"2026-05-12T04:45:00.2545467Z"}</t>
+          <t>status=401 (312ms) :: {"message":"Invalid email or password","errorCode":"UNAUTHORIZED","details":null,"timestamp":"2026-05-12T06:09:58.1487402Z"}</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2331,13 +2331,13 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (0ms) :: </t>
+          <t xml:space="preserve">status=401 (14ms) :: </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>status=200 (53ms) :: [{"agentId":21,"agentCode":"표절-사전-점검-에이전트","agentName":"표절 사전 점검 에이전트","description":"제출 전 논문·과제물의 표절 위험 구절을 사전 탐지하고 수정 방법까지 안내합니다. CopyKill</t>
+          <t>status=200 (52ms) :: [{"agentId":21,"agentCode":"표절-사전-점검-에이전트","agentName":"표절 사전 점검 에이전트","description":"제출 전 논문·과제물의 표절 위험 구절을 사전 탐지하고 수정 방법까지 안내합니다. CopyKill</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2485,22 +2485,18 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>status=415 (12ms) :: {"type":"https://tools.ietf.org/html/rfc9110#section-15.5.16","title":"Unsupported Media Type","status":415,"traceId":"00-2228f487063da7eb6c</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>415: JSON body 필수, 운영 결함 아님 — TC 보정 권장</t>
-        </is>
-      </c>
+          <t>status=200 (36ms) :: {"message":"Logout successful"}</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2549,7 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2695,13 +2691,13 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>status=200 (43ms) :: [{"agentId":21,"agentCode":"표절-사전-점검-에이전트","agentName":"표절 사전 점검 에이전트","description":"제출 전 논문·과제물의 표절 위험 구절을 사전 탐지하고 수정 방법까지 안내합니다. CopyKill</t>
+          <t>status=200 (52ms) :: [{"agentId":21,"agentCode":"표절-사전-점검-에이전트","agentName":"표절 사전 점검 에이전트","description":"제출 전 논문·과제물의 표절 위험 구절을 사전 탐지하고 수정 방법까지 안내합니다. CopyKill</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2750,7 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2803,7 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2856,7 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2909,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2962,7 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3015,7 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3157,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>status=200 (17ms) :: &lt;!DOCTYPE html&gt;
+          <t>status=200 (28ms) :: &lt;!DOCTYPE html&gt;
 &lt;html lang="ko"&gt;
   &lt;head&gt;
     &lt;meta charset="UTF-8"&gt;
@@ -3172,7 +3168,7 @@
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3221,7 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3274,7 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3327,7 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3469,13 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>status=401 (28ms) :: {"message":"API Key is required","hint":"X-API-Key 헤더 또는 Authorization: Bearer &lt;key&gt; 헤더를 포함해주세요."}</t>
+          <t>status=401 (3ms) :: {"message":"API Key is required","hint":"X-API-Key 헤더 또는 Authorization: Bearer &lt;key&gt; 헤더를 포함해주세요."}</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3528,7 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3581,7 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3634,7 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3687,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3740,7 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3793,7 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3941,7 @@
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -3987,22 +3983,18 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=405 (15ms) :: </t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>405: GET 차단 정상 — TC 보정 권장 (POST 필요)</t>
-        </is>
-      </c>
+          <t>status=200 (23ms) :: {"negotiateVersion":1,"connectionId":"ZsyHoe1PVM96BT3viW9oNA","connectionToken":"F7L-kI5cttykt8ylQIMEKA","availableTransports":[{"transport"</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4047,7 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4100,7 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4250,13 +4242,13 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>status=200 (16ms) :: []</t>
+          <t>status=200 (24ms) :: []</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4301,7 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4354,7 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4409,13 +4401,13 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>status=200 (31ms) :: []</t>
+          <t>status=200 (34ms) :: []</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4460,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4608,7 @@
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4663,13 +4655,13 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>status=200 (22ms) :: {"items":[{"id":"52ff0252-d940-4357-8b19-6a1bda9b4cb3","username":"이동건","email":"dglee@idino.co.kr","role":"member","status":"active","organ</t>
+          <t>status=200 (17ms) :: {"items":[{"id":"52ff0252-d940-4357-8b19-6a1bda9b4cb3","username":"이동건","email":"dglee@idino.co.kr","role":"member","status":"active","organ</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4716,13 +4708,13 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (21ms) :: </t>
+          <t xml:space="preserve">status=401 (13ms) :: </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4769,13 +4761,13 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>status=200 (15ms) :: [{"id":"37673e37-ce1e-498e-b493-e3435ffd25ee","organizationId":"00000000-0000-4000-a000-000000000001","parentId":null,"name":"TestDept7","de</t>
+          <t>status=200 (17ms) :: [{"id":"37673e37-ce1e-498e-b493-e3435ffd25ee","organizationId":"00000000-0000-4000-a000-000000000001","parentId":null,"name":"TestDept7","de</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4822,13 +4814,13 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (15ms) :: </t>
+          <t xml:space="preserve">status=401 (13ms) :: </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4875,13 +4867,13 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>status=200 (0ms) :: {"items":[{"id":"c6955ce6-de61-4611-8eff-213c8101d82f","name":"연구과제","description":"연구과제 문서 관리","allowOriginalDownload":false,"organizationI</t>
+          <t>status=200 (5ms) :: {"items":[{"id":"c6955ce6-de61-4611-8eff-213c8101d82f","name":"연구과제","description":"연구과제 문서 관리","allowOriginalDownload":false,"organizationI</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4885,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>dashboard anonymous</t>
+          <t>dashboard anonymous [트랙 #75 보정]</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -4903,7 +4895,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>GET /api/admin/docutil/dashboard/summary</t>
+          <t>GET /api/admin/docutil/dashboard/metrics (+ response-times, search-errors, search-usage, upload-status)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -4923,27 +4915,18 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>status=200 (17ms) :: &lt;!DOCTYPE html&gt;
-&lt;html lang="ko"&gt;
-  &lt;head&gt;
-    &lt;meta charset="UTF-8"&gt;
-    &lt;link rel="icon" href="/favicon.ico"&gt;
-    &lt;meta name="viewport" con</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>[잠재 결함] SPA fallback 200 — 별도 트랙 후보</t>
-        </is>
-      </c>
+          <t xml:space="preserve">status=401 (26ms) :: </t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4938,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>dashboard admin read</t>
+          <t>dashboard admin read [트랙 #75 보정]</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -4965,7 +4948,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>GET /api/admin/docutil/dashboard/summary</t>
+          <t>GET /api/admin/docutil/dashboard/metrics 외 4개</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -4990,18 +4973,13 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>status=200 (15ms) :: &lt;!DOCTYPE html&gt;
-&lt;html lang="ko"&gt;
-  &lt;head&gt;
-    &lt;meta charset="UTF-8"&gt;
-    &lt;link rel="icon" href="/favicon.ico"&gt;
-    &lt;meta name="viewport" con</t>
+          <t>status=200 (15ms) :: {"totalUsers":11,"activeUsers":10,"totalDocuments":31,"totalSearches":110,"featureUsage":{"user":110,"assistant":110}}</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5032,7 @@
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5101,13 +5079,13 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>status=200 (25ms) :: {"items":[{"id":"37e46a26-f216-4b60-8538-eaf4145a8ddd","organizationId":"00000000-0000-4000-a000-000000000001","userId":"bafe866b-b7e2-4d26-</t>
+          <t>status=200 (28ms) :: {"items":[{"id":"37e46a26-f216-4b60-8538-eaf4145a8ddd","organizationId":"00000000-0000-4000-a000-000000000001","userId":"bafe866b-b7e2-4d26-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5154,13 +5132,13 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (16ms) :: </t>
+          <t xml:space="preserve">status=401 (27ms) :: </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5207,13 +5185,13 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>status=200 (15ms) :: {"items":[{"id":"8a0f9f0f-c195-4a96-822c-f3fd7173e4b3","name":"기본 범위 TEST","description":"default","organizationId":"00000000-0000-4000-a000</t>
+          <t>status=200 (16ms) :: {"items":[{"id":"8a0f9f0f-c195-4a96-822c-f3fd7173e4b3","name":"기본 범위 TEST","description":"default","organizationId":"00000000-0000-4000-a000</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5203,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>evaluation anonymous</t>
+          <t>evaluation anonymous [트랙 #75 보정]</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -5235,7 +5213,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>GET /api/admin/docutil/evaluation</t>
+          <t>GET /api/admin/docutil/evaluation/config</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -5255,27 +5233,18 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>status=200 (16ms) :: &lt;!DOCTYPE html&gt;
-&lt;html lang="ko"&gt;
-  &lt;head&gt;
-    &lt;meta charset="UTF-8"&gt;
-    &lt;link rel="icon" href="/favicon.ico"&gt;
-    &lt;meta name="viewport" con</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>[잠재 결함] SPA fallback 200 — 별도 트랙 후보</t>
-        </is>
-      </c>
+          <t xml:space="preserve">status=401 (13ms) :: </t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5256,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>evaluation admin read</t>
+          <t>evaluation admin read [트랙 #75 보정]</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -5297,7 +5266,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>GET /api/admin/docutil/evaluation</t>
+          <t>GET /api/admin/docutil/evaluation/config</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -5322,18 +5291,13 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>status=200 (15ms) :: &lt;!DOCTYPE html&gt;
-&lt;html lang="ko"&gt;
-  &lt;head&gt;
-    &lt;meta charset="UTF-8"&gt;
-    &lt;link rel="icon" href="/favicon.ico"&gt;
-    &lt;meta name="viewport" con</t>
+          <t>status=200 (16ms) :: {"id":"15fd5542-200a-48c1-9eb5-d502443a62fb","organizationId":"00000000-0000-4000-a000-000000000001","contextRelevancyWeight":0.25,"answerFa</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5380,13 +5344,13 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (18ms) :: </t>
+          <t xml:space="preserve">status=401 (14ms) :: </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5433,13 +5397,13 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>status=200 (26ms) :: {"items":[],"total":0,"page":1,"size":20}</t>
+          <t>status=200 (17ms) :: {"items":[],"total":0,"page":1,"size":20}</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5486,13 +5450,13 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (16ms) :: </t>
+          <t xml:space="preserve">status=401 (12ms) :: </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5539,13 +5503,13 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>status=200 (16ms) :: {"items":[{"id":"b2af009f-9018-43f5-9aac-44d5320a8ed3","templateId":null,"organizationId":"00000000-0000-4000-a000-000000000001","title":"회의</t>
+          <t>status=200 (20ms) :: {"items":[{"id":"b2af009f-9018-43f5-9aac-44d5320a8ed3","templateId":null,"organizationId":"00000000-0000-4000-a000-000000000001","title":"회의</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5592,13 +5556,13 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (32ms) :: </t>
+          <t xml:space="preserve">status=401 (29ms) :: </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5645,13 +5609,13 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>status=200 (25ms) :: {"items":[{"id":"b1a2264a-24a1-48a8-8ef4-57ba47378a70","organizationId":"00000000-0000-4000-a000-000000000001","name":"회의록_양식","description"</t>
+          <t>status=200 (4ms) :: {"items":[{"id":"b1a2264a-24a1-48a8-8ef4-57ba47378a70","organizationId":"00000000-0000-4000-a000-000000000001","name":"회의록_양식","description"</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5698,13 +5662,13 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (16ms) :: </t>
+          <t xml:space="preserve">status=401 (25ms) :: </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5751,13 +5715,13 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>status=200 (24ms) :: {"items":[{"id":"ae43f053-2279-48b7-85ea-56ba9c4bfabd","organizationId":"00000000-0000-4000-a000-000000000001","llmName":"openai","apiKeyPre</t>
+          <t>status=200 (33ms) :: {"items":[{"id":"ae43f053-2279-48b7-85ea-56ba9c4bfabd","organizationId":"00000000-0000-4000-a000-000000000001","llmName":"openai","apiKeyPre</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5768,13 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (11ms) :: </t>
+          <t xml:space="preserve">status=401 (27ms) :: </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5857,13 +5821,13 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>status=200 (15ms) :: {"items":[{"id":"e90df318-70de-4137-b1ba-ea15cb54c52a","organizationId":"00000000-0000-4000-a000-000000000001","name":"회의록 작성 AI","descripti</t>
+          <t>status=200 (6ms) :: {"items":[{"id":"e90df318-70de-4137-b1ba-ea15cb54c52a","organizationId":"00000000-0000-4000-a000-000000000001","name":"회의록 작성 AI","descripti</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5910,13 +5874,13 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (17ms) :: </t>
+          <t xml:space="preserve">status=401 (23ms) :: </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -5963,13 +5927,13 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>status=200 (43ms) :: {"items":[{"id":"becafc95-f07f-4f8c-984d-ba83481257b9","organizationId":"00000000-0000-4000-a000-000000000001","generatedByUserId":"00000000</t>
+          <t>status=200 (41ms) :: {"items":[{"id":"becafc95-f07f-4f8c-984d-ba83481257b9","organizationId":"00000000-0000-4000-a000-000000000001","generatedByUserId":"00000000</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -6111,13 +6075,13 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>status=200 (16ms) :: [{"serviceId":17,"serviceName":"ChatGPT","date":"2026-05-10T00:00:00Z","requestCount":1,"totalTokens":559,"totalCost":0.0168,"averageRespons</t>
+          <t>status=200 (35ms) :: [{"serviceId":17,"serviceName":"ChatGPT","date":"2026-05-10T00:00:00Z","requestCount":1,"totalTokens":559,"totalCost":0.0168,"averageRespons</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -6164,13 +6128,13 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>status=200 (187ms) :: [{"quotaId":4,"userId":1,"userEmail":"admin@example.com","serviceId":20,"serviceName":"Copilot","monthlyLimit":2000,"monthlyTokenLimit":null</t>
+          <t>status=200 (207ms) :: [{"quotaId":4,"userId":1,"userEmail":"admin@example.com","serviceId":20,"serviceName":"Copilot","monthlyLimit":2000,"monthlyTokenLimit":null</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6181,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>status=200 (16ms) :: &lt;!DOCTYPE html&gt;
+          <t>status=200 (27ms) :: &lt;!DOCTYPE html&gt;
 &lt;html lang="ko"&gt;
   &lt;head&gt;
     &lt;meta charset="UTF-8"&gt;
@@ -6228,7 +6192,7 @@
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 13:45:00</t>
+          <t>2026-05-12 15:09:58</t>
         </is>
       </c>
     </row>

--- a/docs/TEST_CHECKLIST.xlsx
+++ b/docs/TEST_CHECKLIST.xlsx
@@ -1092,13 +1092,17 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: DocUtil 사용자 비번 미보유</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] DocUtil admin 자격증명 미확보</t>
+        </is>
+      </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1149,17 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: LLM 비용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] I-01 의존</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -1198,13 +1206,17 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: DocUtil 인증 필요</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] I-01 의존</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -1251,13 +1263,17 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 mutation + 저장공간</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] I-01 의존 + 운영 mutation</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -1304,13 +1320,17 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: LLM 비용</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] I-01 의존 + LLM 비용</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -1558,13 +1578,17 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 비 admin 계정 미보유</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] 비 admin 자격증명 미보유</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -1611,13 +1635,17 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 부하 회피 — 별도 환경</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>(2495ms) 70회 시도, 429 발견=False, statuses[-5:]=[200, 200, 200, 200, 200] (2495ms)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] 70회 모두 200 — Rate Limit 한도 더 크거나 정책 비활성</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -1664,13 +1692,17 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">status=401 (3ms) :: </t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>status=401 (15ms) ::  (15ms)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] 유효한 JWT 아니므로 401/403 기대</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -1712,18 +1744,22 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 DB 영향 가능성 — 별도 환경</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>status=200 (22ms) payload='' OR 1=1--' (22ms)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] safe — 0건 반환 (정상 search 동작)</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -1765,18 +1801,22 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: UI 의존</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t>status=200 (17ms) payload='&lt;script&gt;alert(1)&lt;/script&gt;' (17ms)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] JSON API 응답 — XSS 컨텍스트 없음 (HTML 렌더링은 클라이언트 책임)</t>
+        </is>
+      </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -2024,13 +2064,17 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: LLM 비용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] I-01 의존</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -2077,13 +2121,17 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 mutation</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] DocUtil 자격증명 + 운영 mutation</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -2437,13 +2485,17 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 mutation 회피 — 별도 토큰 발급 부담</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] refresh token 자동화 우회 비용</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -2543,13 +2595,17 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 추가 자격증명 미보유, 사용자 결정 필요</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] 추가 admin 자격증명 미보유</t>
+        </is>
+      </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -2792,18 +2848,22 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 mutation 위험, 사용자 결정 필요</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>status=201 (24ms) agentId=41 :: {"agentId":41,"agentCode":"test-track84-1778571525","agentName":"Track84 Test Agent 1778571525","description (24ms)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] cleanup=OK (DELETE=204, GET=404)</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -2845,18 +2905,22 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 mutation 위험</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>PUT=200 (41ms) GET=200 reflected=True (41ms)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[트랙 #84 갱신] </t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -2898,18 +2962,22 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 mutation 위험</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>PUT1=200 hybrid_set=True PUT2=200 (60ms)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[트랙 #84 갱신] </t>
+        </is>
+      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -2951,18 +3019,22 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 mutation 위험</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t>PUT1=200 set=True PUT2=200 (90ms)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[트랙 #84 갱신] </t>
+        </is>
+      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -3004,18 +3076,22 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 mutation 위험</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t>PUT1=200 rag_on=True PUT2=200 (154ms)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[트랙 #84 갱신] </t>
+        </is>
+      </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -3517,18 +3593,22 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 LLM 비용 발생 — 사용자 명시 후 1회 실행 권장</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>status=200 (72ms) model=표절-사전-점검-에이전트 :: {"id":"chatcmpl-1d7df29b5de446beb8145403404240fc","object":"chat.completion","created":1778571524," (72ms)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] LLM 비용 발생 (~$0.0001) — max_tokens=5</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -3570,18 +3650,22 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 LLM 비용 발생</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>status=200 (820ms) chunks=7 [DONE]=True (820ms)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] LLM 비용 발생 (~$0.0001) + SSE [DONE] 검증</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -3681,13 +3765,17 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: DALL-E 비용 발생 — 사용자 결정</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>status=405 (15ms) — ApiKey 가 image-generator agent 권한 없음 (15ms)</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] docutil-image-generator agent 전용 ApiKey 필요 (별도 트랙)</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -3734,13 +3822,17 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: Nexus 인스턴스 가용성 의존 — 별도 환경</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
+          <t xml:space="preserve"> (0ms)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] Nexus 인스턴스 미부팅 (192.168.22.28 GPU 호스트 — TECHSPEC §16 R23)</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -3782,18 +3874,22 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: PII 시드 데이터 입력 부담</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
+          <t>status=200 (108ms) agentCode=career-actionboard-orchestrator :: {"id":"chatcmpl-43b4d5f9bf8f4c1181d89543918b90cd","object":"chat.completion" (108ms)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] LLM 비용 (~$0.0001 또는 차단=0) — Hybrid agent 인지 검증</t>
+        </is>
+      </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -3930,18 +4026,22 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 LLM 비용 발생</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
+          <t>status=200 (893ms) agentId=21 rag=False :: {"messageId":912,"conversationId":264,"content":"","model":"gpt-5-2025-08-07","tokensUsed":243,"c (893ms)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] LLM 비용 (~$0.001 RAG 포함) — agent=21</t>
+        </is>
+      </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -4041,13 +4141,17 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 LLM 비용</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>status=405 (14ms) agentCode=표절-사전-점검-에이전트 ::  (14ms)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] 공개 챗봇 endpoint 형식 다름 (status=405)</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -4089,18 +4193,22 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 LLM 비용</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>status=400 (60ms) agentId=21 :: {"message":"메시지에 개인정보가 포함되어 있습니다: 휴대폰 번호, 주민등록번호, 신용카드 번호, 계좌번호","errorCode":"PII_DETECTED","details":{"dete (60ms)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] 차단 PASS (LLM 비용 0)</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -4290,18 +4398,22 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: 운영 mutation</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>status=201 (149ms) toolId=8 (149ms)</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>[트랙 #84 갱신] cleanup=OK (DELETE=204, GET=404)</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
@@ -4343,18 +4455,22 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>status= (ms) :: LLM 비용 + side effect</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>status=200 (91ms) :: {"executionId":7,"toolId":8,"toolName":"test-track84-tool-1778571525","versionId":7,"version":"1.0","userId":1,"inputDa (91ms)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[트랙 #84 갱신] </t>
+        </is>
+      </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12 15:09:58</t>
+          <t>2026-05-12 16:38:48</t>
         </is>
       </c>
     </row>
